--- a/primers_example_database.xlsx
+++ b/primers_example_database.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8580"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="geneann" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ID order</t>
   </si>
@@ -47,6 +47,9 @@
     <t>chain</t>
   </si>
   <si>
+    <t>chr</t>
+  </si>
+  <si>
     <t>grch37_start_coordinates</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
   </si>
   <si>
     <t>+</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
   <si>
     <t>pomogite1</t>
@@ -1246,20 +1252,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="10.8888888888889"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="35.8888888888889" customWidth="1"/>
-    <col min="6" max="6" width="7.88888888888889" customWidth="1"/>
-    <col min="7" max="7" width="29.4444444444444" customWidth="1"/>
-    <col min="8" max="8" width="26.1111111111111" customWidth="1"/>
-    <col min="9" max="9" width="21.1111111111111" customWidth="1"/>
-    <col min="10" max="10" width="22.7777777777778" customWidth="1"/>
+    <col min="6" max="7" width="7.88888888888889" customWidth="1"/>
+    <col min="8" max="8" width="29.4444444444444" customWidth="1"/>
+    <col min="9" max="9" width="26.1111111111111" customWidth="1"/>
+    <col min="10" max="10" width="21.1111111111111" customWidth="1"/>
+    <col min="11" max="11" width="22.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1290,8 +1296,11 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="2">
         <v>3416</v>
       </c>
@@ -1299,31 +1308,34 @@
         <v>46644</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1">
         <v>123456789</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>123456790</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>123456791</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>123456792</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="2">
         <v>3416</v>
       </c>
@@ -1331,94 +1343,97 @@
         <v>46645</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1">
         <v>123456790</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>123456791</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>123456792</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>123456793</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
+    <row r="4" s="1" customFormat="1" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
+    <row r="5" s="1" customFormat="1" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:10">
+    <row r="6" s="1" customFormat="1" spans="1:11">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:10">
+    <row r="7" s="1" customFormat="1" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:10">
+    <row r="8" s="1" customFormat="1" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:10">
+    <row r="9" s="1" customFormat="1" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:10">
+    <row r="10" s="1" customFormat="1" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:10">
+    <row r="11" s="1" customFormat="1" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:10">
+    <row r="12" s="1" customFormat="1" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:10">
+    <row r="13" s="1" customFormat="1" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
